--- a/docs/StructureDefinition-average-blood-pressure.xlsx
+++ b/docs/StructureDefinition-average-blood-pressure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.6</t>
+    <t>0.5.8</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/StructureDefinition-average-blood-pressure.xlsx
+++ b/docs/StructureDefinition-average-blood-pressure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.8</t>
+    <t>0.5.9</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/StructureDefinition-average-blood-pressure.xlsx
+++ b/docs/StructureDefinition-average-blood-pressure.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3916" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3916" uniqueCount="644">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.12</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -482,6 +482,10 @@
   </si>
   <si>
     <t>The position of the body when the observation was done, e.g. standing, sitting. To be used only when the body position in not precoordinated in the observation code.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
   </si>
   <si>
     <t>Observation.extension:exerciseAssociation</t>
@@ -3578,7 +3582,7 @@
         <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>144</v>
@@ -3604,13 +3608,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>137</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>20</v>
@@ -3632,10 +3636,10 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M11" t="s" s="2">
         <v>140</v>
@@ -3724,13 +3728,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>137</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>20</v>
@@ -3752,10 +3756,10 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M12" t="s" s="2">
         <v>140</v>
@@ -3844,13 +3848,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>137</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>20</v>
@@ -3872,10 +3876,10 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
         <v>140</v>
@@ -3964,14 +3968,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3993,16 +3997,16 @@
         <v>138</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -4051,7 +4055,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -4086,10 +4090,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4112,17 +4116,17 @@
         <v>94</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>20</v>
@@ -4171,7 +4175,7 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -4186,19 +4190,19 @@
         <v>105</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>20</v>
@@ -4206,14 +4210,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4232,17 +4236,17 @@
         <v>94</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -4291,7 +4295,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -4306,16 +4310,16 @@
         <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>20</v>
@@ -4326,14 +4330,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4352,16 +4356,16 @@
         <v>94</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4411,7 +4415,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4426,16 +4430,16 @@
         <v>105</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>20</v>
@@ -4446,10 +4450,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4475,16 +4479,16 @@
         <v>113</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -4509,11 +4513,11 @@
         <v>20</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>20</v>
@@ -4531,7 +4535,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>93</v>
@@ -4546,19 +4550,19 @@
         <v>105</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>20</v>
@@ -4566,10 +4570,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4592,19 +4596,19 @@
         <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -4632,16 +4636,16 @@
         <v>117</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC19" s="2"/>
       <c r="AD19" t="s" s="2">
@@ -4651,7 +4655,7 @@
         <v>142</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4675,10 +4679,10 @@
         <v>20</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>20</v>
@@ -4686,13 +4690,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>20</v>
@@ -4714,19 +4718,19 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -4754,10 +4758,10 @@
         <v>117</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>20</v>
@@ -4775,7 +4779,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4799,10 +4803,10 @@
         <v>20</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>20</v>
@@ -4810,10 +4814,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4836,13 +4840,13 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4893,7 +4897,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4917,7 +4921,7 @@
         <v>20</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>20</v>
@@ -4928,14 +4932,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4957,13 +4961,13 @@
         <v>138</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -5004,7 +5008,7 @@
         <v>141</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>20</v>
@@ -5013,7 +5017,7 @@
         <v>142</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -5037,7 +5041,7 @@
         <v>20</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>20</v>
@@ -5048,10 +5052,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5074,19 +5078,19 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -5135,7 +5139,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5156,10 +5160,10 @@
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>20</v>
@@ -5170,10 +5174,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5196,13 +5200,13 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5253,7 +5257,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -5277,7 +5281,7 @@
         <v>20</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>20</v>
@@ -5288,14 +5292,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5317,13 +5321,13 @@
         <v>138</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5364,7 +5368,7 @@
         <v>141</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>20</v>
@@ -5373,7 +5377,7 @@
         <v>142</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5397,7 +5401,7 @@
         <v>20</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>20</v>
@@ -5408,10 +5412,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5437,23 +5441,23 @@
         <v>107</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>20</v>
@@ -5495,7 +5499,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5516,10 +5520,10 @@
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>20</v>
@@ -5530,10 +5534,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5556,16 +5560,16 @@
         <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5615,7 +5619,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5636,10 +5640,10 @@
         <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>20</v>
@@ -5650,10 +5654,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5679,21 +5683,21 @@
         <v>113</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>20</v>
@@ -5735,7 +5739,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5756,10 +5760,10 @@
         <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>20</v>
@@ -5770,10 +5774,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5796,17 +5800,17 @@
         <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5855,7 +5859,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5876,10 +5880,10 @@
         <v>20</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
@@ -5890,10 +5894,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5916,19 +5920,19 @@
         <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5977,7 +5981,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5998,10 +6002,10 @@
         <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>20</v>
@@ -6012,10 +6016,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6038,19 +6042,19 @@
         <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -6099,7 +6103,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -6120,10 +6124,10 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
@@ -6134,14 +6138,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -6160,19 +6164,19 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -6182,7 +6186,7 @@
         <v>20</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>20</v>
@@ -6197,13 +6201,13 @@
         <v>20</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>20</v>
@@ -6221,7 +6225,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>93</v>
@@ -6236,30 +6240,30 @@
         <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6282,19 +6286,19 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -6343,7 +6347,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6358,19 +6362,19 @@
         <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>20</v>
@@ -6378,10 +6382,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6404,16 +6408,16 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6463,7 +6467,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6484,13 +6488,13 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>20</v>
@@ -6498,14 +6502,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6524,19 +6528,19 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -6585,7 +6589,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6600,19 +6604,19 @@
         <v>105</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>20</v>
@@ -6620,14 +6624,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6646,19 +6650,19 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6707,7 +6711,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6716,25 +6720,25 @@
         <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>20</v>
@@ -6742,10 +6746,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6768,16 +6772,16 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6827,7 +6831,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6848,13 +6852,13 @@
         <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>20</v>
@@ -6862,10 +6866,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6888,17 +6892,17 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6947,7 +6951,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6962,19 +6966,19 @@
         <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>20</v>
@@ -6982,10 +6986,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7008,19 +7012,19 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -7069,7 +7073,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7078,7 +7082,7 @@
         <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>105</v>
@@ -7087,27 +7091,27 @@
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7130,19 +7134,19 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -7167,13 +7171,13 @@
         <v>20</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>20</v>
@@ -7191,7 +7195,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7200,7 +7204,7 @@
         <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>105</v>
@@ -7215,7 +7219,7 @@
         <v>136</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>20</v>
@@ -7226,14 +7230,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7252,19 +7256,19 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -7289,13 +7293,13 @@
         <v>20</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
@@ -7313,7 +7317,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7331,27 +7335,27 @@
         <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7374,19 +7378,19 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -7435,7 +7439,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7456,10 +7460,10 @@
         <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>20</v>
@@ -7470,10 +7474,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7496,16 +7500,16 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7531,13 +7535,13 @@
         <v>20</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>20</v>
@@ -7555,7 +7559,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7573,27 +7577,27 @@
         <v>20</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7616,19 +7620,19 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7653,13 +7657,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -7677,7 +7681,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7698,10 +7702,10 @@
         <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>20</v>
@@ -7712,10 +7716,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7738,16 +7742,16 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7797,7 +7801,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7815,27 +7819,27 @@
         <v>20</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7858,16 +7862,16 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7917,7 +7921,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7935,27 +7939,27 @@
         <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7978,19 +7982,19 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -8039,7 +8043,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8051,7 +8055,7 @@
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>20</v>
@@ -8060,10 +8064,10 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
@@ -8074,10 +8078,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8100,13 +8104,13 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8157,7 +8161,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8181,7 +8185,7 @@
         <v>20</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>20</v>
@@ -8192,14 +8196,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -8221,13 +8225,13 @@
         <v>138</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8277,7 +8281,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8301,7 +8305,7 @@
         <v>20</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>20</v>
@@ -8312,14 +8316,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8341,16 +8345,16 @@
         <v>138</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -8399,7 +8403,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8434,10 +8438,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8460,13 +8464,13 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8517,7 +8521,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8526,7 +8530,7 @@
         <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>105</v>
@@ -8538,10 +8542,10 @@
         <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>20</v>
@@ -8552,10 +8556,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8578,13 +8582,13 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8635,7 +8639,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8644,7 +8648,7 @@
         <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>105</v>
@@ -8656,10 +8660,10 @@
         <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
@@ -8670,10 +8674,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8696,19 +8700,19 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8736,10 +8740,10 @@
         <v>117</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>20</v>
@@ -8757,7 +8761,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8775,13 +8779,13 @@
         <v>20</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
@@ -8792,10 +8796,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8818,19 +8822,19 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8855,13 +8859,13 @@
         <v>20</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>20</v>
@@ -8879,7 +8883,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8897,13 +8901,13 @@
         <v>20</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>20</v>
@@ -8914,10 +8918,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8940,17 +8944,17 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8999,7 +9003,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9023,7 +9027,7 @@
         <v>20</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>20</v>
@@ -9034,10 +9038,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9060,13 +9064,13 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9117,7 +9121,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9138,10 +9142,10 @@
         <v>20</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>20</v>
@@ -9152,10 +9156,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9178,16 +9182,16 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9237,7 +9241,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9258,10 +9262,10 @@
         <v>20</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>20</v>
@@ -9272,10 +9276,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9298,16 +9302,16 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9357,7 +9361,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9378,10 +9382,10 @@
         <v>20</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>20</v>
@@ -9392,10 +9396,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9418,19 +9422,19 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -9467,7 +9471,7 @@
         <v>20</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AC59" s="2"/>
       <c r="AD59" t="s" s="2">
@@ -9477,7 +9481,7 @@
         <v>142</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9489,7 +9493,7 @@
         <v>20</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>20</v>
@@ -9498,10 +9502,10 @@
         <v>20</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>20</v>
@@ -9512,10 +9516,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9538,13 +9542,13 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9595,7 +9599,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9619,7 +9623,7 @@
         <v>20</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>20</v>
@@ -9630,14 +9634,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9659,13 +9663,13 @@
         <v>138</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9715,7 +9719,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9739,7 +9743,7 @@
         <v>20</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>20</v>
@@ -9750,14 +9754,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9779,16 +9783,16 @@
         <v>138</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -9837,7 +9841,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9872,10 +9876,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9898,19 +9902,19 @@
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -9935,13 +9939,13 @@
         <v>20</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>20</v>
@@ -9959,7 +9963,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>93</v>
@@ -9977,16 +9981,16 @@
         <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>20</v>
@@ -9994,10 +9998,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10020,19 +10024,19 @@
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -10057,13 +10061,13 @@
         <v>20</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>20</v>
@@ -10081,7 +10085,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10090,7 +10094,7 @@
         <v>93</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>105</v>
@@ -10099,27 +10103,27 @@
         <v>20</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10142,19 +10146,19 @@
         <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>20</v>
@@ -10179,13 +10183,13 @@
         <v>20</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>20</v>
@@ -10203,7 +10207,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10212,7 +10216,7 @@
         <v>93</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>105</v>
@@ -10227,7 +10231,7 @@
         <v>136</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>20</v>
@@ -10238,14 +10242,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10264,19 +10268,19 @@
         <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -10301,13 +10305,13 @@
         <v>20</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>20</v>
@@ -10325,7 +10329,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10343,27 +10347,27 @@
         <v>20</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10389,16 +10393,16 @@
         <v>20</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -10447,7 +10451,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10468,10 +10472,10 @@
         <v>20</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>20</v>
@@ -10482,13 +10486,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>20</v>
@@ -10510,19 +10514,19 @@
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -10571,7 +10575,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10583,7 +10587,7 @@
         <v>20</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>20</v>
@@ -10592,10 +10596,10 @@
         <v>20</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>20</v>
@@ -10606,10 +10610,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10632,13 +10636,13 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10689,7 +10693,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10713,7 +10717,7 @@
         <v>20</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>20</v>
@@ -10724,14 +10728,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10753,13 +10757,13 @@
         <v>138</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10809,7 +10813,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10833,7 +10837,7 @@
         <v>20</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>20</v>
@@ -10844,14 +10848,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10873,16 +10877,16 @@
         <v>138</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>20</v>
@@ -10931,7 +10935,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10966,10 +10970,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10992,19 +10996,19 @@
         <v>94</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>20</v>
@@ -11014,7 +11018,7 @@
         <v>20</v>
       </c>
       <c r="S72" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="T72" t="s" s="2">
         <v>20</v>
@@ -11029,13 +11033,13 @@
         <v>20</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>20</v>
@@ -11053,7 +11057,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>93</v>
@@ -11071,16 +11075,16 @@
         <v>20</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>20</v>
@@ -11088,10 +11092,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11114,19 +11118,19 @@
         <v>94</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>20</v>
@@ -11151,29 +11155,29 @@
         <v>20</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AC73" s="2"/>
       <c r="AD73" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11182,7 +11186,7 @@
         <v>93</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>105</v>
@@ -11191,30 +11195,30 @@
         <v>20</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D74" t="s" s="2">
         <v>20</v>
@@ -11236,19 +11240,19 @@
         <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>20</v>
@@ -11273,13 +11277,13 @@
         <v>20</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>20</v>
@@ -11297,7 +11301,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11306,7 +11310,7 @@
         <v>93</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>105</v>
@@ -11315,27 +11319,27 @@
         <v>20</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11358,13 +11362,13 @@
         <v>20</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11415,7 +11419,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11439,7 +11443,7 @@
         <v>20</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>20</v>
@@ -11450,14 +11454,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11479,13 +11483,13 @@
         <v>138</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11526,7 +11530,7 @@
         <v>141</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>20</v>
@@ -11535,7 +11539,7 @@
         <v>142</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11559,7 +11563,7 @@
         <v>20</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>20</v>
@@ -11570,10 +11574,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11596,19 +11600,19 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>20</v>
@@ -11657,7 +11661,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11678,10 +11682,10 @@
         <v>20</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>20</v>
@@ -11692,10 +11696,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11721,20 +11725,20 @@
         <v>113</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q78" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="R78" t="s" s="2">
         <v>20</v>
@@ -11755,13 +11759,13 @@
         <v>20</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>20</v>
@@ -11779,7 +11783,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11800,10 +11804,10 @@
         <v>20</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>20</v>
@@ -11814,10 +11818,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11840,17 +11844,17 @@
         <v>94</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>20</v>
@@ -11899,7 +11903,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11920,10 +11924,10 @@
         <v>20</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>20</v>
@@ -11934,10 +11938,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11963,21 +11967,21 @@
         <v>107</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q80" s="2"/>
       <c r="R80" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="S80" t="s" s="2">
         <v>20</v>
@@ -12019,7 +12023,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12028,7 +12032,7 @@
         <v>93</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>105</v>
@@ -12040,10 +12044,10 @@
         <v>20</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>20</v>
@@ -12054,10 +12058,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12083,23 +12087,23 @@
         <v>113</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="S81" t="s" s="2">
         <v>20</v>
@@ -12141,7 +12145,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12162,10 +12166,10 @@
         <v>20</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>20</v>
@@ -12176,10 +12180,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12202,19 +12206,19 @@
         <v>20</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>20</v>
@@ -12239,13 +12243,13 @@
         <v>20</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>20</v>
@@ -12263,7 +12267,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12272,7 +12276,7 @@
         <v>93</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>105</v>
@@ -12287,7 +12291,7 @@
         <v>136</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>20</v>
@@ -12298,14 +12302,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12324,19 +12328,19 @@
         <v>20</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>20</v>
@@ -12361,13 +12365,13 @@
         <v>20</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>20</v>
@@ -12385,7 +12389,7 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12403,27 +12407,27 @@
         <v>20</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12449,16 +12453,16 @@
         <v>20</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>20</v>
@@ -12507,7 +12511,7 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12528,10 +12532,10 @@
         <v>20</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>20</v>
@@ -12542,13 +12546,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D85" t="s" s="2">
         <v>20</v>
@@ -12570,19 +12574,19 @@
         <v>94</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>20</v>
@@ -12631,7 +12635,7 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12643,7 +12647,7 @@
         <v>20</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>20</v>
@@ -12652,10 +12656,10 @@
         <v>20</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>20</v>
@@ -12666,10 +12670,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12692,13 +12696,13 @@
         <v>20</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12749,7 +12753,7 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12773,7 +12777,7 @@
         <v>20</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>20</v>
@@ -12784,14 +12788,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12813,13 +12817,13 @@
         <v>138</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12869,7 +12873,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12893,7 +12897,7 @@
         <v>20</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>20</v>
@@ -12904,14 +12908,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12933,16 +12937,16 @@
         <v>138</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>20</v>
@@ -12991,7 +12995,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13026,10 +13030,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13052,19 +13056,19 @@
         <v>94</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>20</v>
@@ -13074,7 +13078,7 @@
         <v>20</v>
       </c>
       <c r="S89" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="T89" t="s" s="2">
         <v>20</v>
@@ -13089,13 +13093,13 @@
         <v>20</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>20</v>
@@ -13113,7 +13117,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>93</v>
@@ -13131,16 +13135,16 @@
         <v>20</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>20</v>
@@ -13148,10 +13152,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13174,19 +13178,19 @@
         <v>94</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>20</v>
@@ -13211,29 +13215,29 @@
         <v>20</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AC90" s="2"/>
       <c r="AD90" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13242,7 +13246,7 @@
         <v>93</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>105</v>
@@ -13251,30 +13255,30 @@
         <v>20</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D91" t="s" s="2">
         <v>20</v>
@@ -13296,19 +13300,19 @@
         <v>94</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>20</v>
@@ -13333,13 +13337,13 @@
         <v>20</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>20</v>
@@ -13357,7 +13361,7 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13366,7 +13370,7 @@
         <v>93</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>105</v>
@@ -13375,27 +13379,27 @@
         <v>20</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13418,13 +13422,13 @@
         <v>20</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13475,7 +13479,7 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13499,7 +13503,7 @@
         <v>20</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>20</v>
@@ -13510,14 +13514,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13539,13 +13543,13 @@
         <v>138</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13586,7 +13590,7 @@
         <v>141</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>20</v>
@@ -13595,7 +13599,7 @@
         <v>142</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13619,7 +13623,7 @@
         <v>20</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>20</v>
@@ -13630,10 +13634,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13656,19 +13660,19 @@
         <v>94</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>20</v>
@@ -13717,7 +13721,7 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13738,10 +13742,10 @@
         <v>20</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>20</v>
@@ -13752,10 +13756,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13781,20 +13785,20 @@
         <v>113</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q95" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="R95" t="s" s="2">
         <v>20</v>
@@ -13815,13 +13819,13 @@
         <v>20</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>20</v>
@@ -13839,7 +13843,7 @@
         <v>20</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13860,10 +13864,10 @@
         <v>20</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>20</v>
@@ -13874,10 +13878,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13900,17 +13904,17 @@
         <v>94</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>20</v>
@@ -13959,7 +13963,7 @@
         <v>20</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13980,10 +13984,10 @@
         <v>20</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>20</v>
@@ -13994,10 +13998,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14023,21 +14027,21 @@
         <v>107</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="S97" t="s" s="2">
         <v>20</v>
@@ -14079,7 +14083,7 @@
         <v>20</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -14088,7 +14092,7 @@
         <v>93</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>105</v>
@@ -14100,10 +14104,10 @@
         <v>20</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>20</v>
@@ -14114,10 +14118,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14143,23 +14147,23 @@
         <v>113</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q98" s="2"/>
       <c r="R98" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="S98" t="s" s="2">
         <v>20</v>
@@ -14201,7 +14205,7 @@
         <v>20</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14222,10 +14226,10 @@
         <v>20</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>20</v>
@@ -14236,10 +14240,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14262,19 +14266,19 @@
         <v>20</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>20</v>
@@ -14299,13 +14303,13 @@
         <v>20</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>20</v>
@@ -14323,7 +14327,7 @@
         <v>20</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14332,7 +14336,7 @@
         <v>93</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>105</v>
@@ -14347,7 +14351,7 @@
         <v>136</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>20</v>
@@ -14358,14 +14362,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -14384,19 +14388,19 @@
         <v>20</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>20</v>
@@ -14421,13 +14425,13 @@
         <v>20</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>20</v>
@@ -14445,7 +14449,7 @@
         <v>20</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -14463,27 +14467,27 @@
         <v>20</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14509,16 +14513,16 @@
         <v>20</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>20</v>
@@ -14567,7 +14571,7 @@
         <v>20</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -14588,10 +14592,10 @@
         <v>20</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>20</v>

--- a/docs/StructureDefinition-average-blood-pressure.xlsx
+++ b/docs/StructureDefinition-average-blood-pressure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
